--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>45845</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>44476</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46100</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>44909</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>46063</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>44957</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>45750</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45755</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>46100</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>46125</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44543</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>44594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>45694</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45540</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>46141</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>45916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45989</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>46163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>46108</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45845</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>45989</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>44818</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>44593</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45478</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45427</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46141</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>46154</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>46154</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>46163</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>46163</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>46175</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>46175</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>46190</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>46125</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>45692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45231</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>46224</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45195</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44817</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45663</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>45623</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>44671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46141</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44699</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44795</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>44819</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>44719</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>44792</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>44721</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>44606</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44515</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44871</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44525</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44792</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44812</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>44616</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>44750</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44754</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44590</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44708</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44762</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44782</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44907</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>45624</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45572</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44560</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45007</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45335</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45201</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45238</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45027</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45483</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44543</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>44806</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45544</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>45145</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45450</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44657</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44924</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44525</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45681</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45037</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45730</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44515</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45187</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44754</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45217</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45162</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44832</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44954</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45055</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45412</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45642</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44817</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45434</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45715</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>44663</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>45635</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44923</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45481</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45068</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45932</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45987</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45987</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45764</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45601</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45309</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>45077</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44868</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45845</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>45839</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45691</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45845</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>46136</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45201</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45567</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45763</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45710</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45755</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45932</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45845</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>44804</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>44979</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45334</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>46141</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44852</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45399</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45201</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46142</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45666</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45548</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45238</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46149</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>46149</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45946</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45946</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45946</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>44930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45932</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45643</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44613</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45954</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45954</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45755</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45959</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45961</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45959</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44613</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45372</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46148</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45493</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45201</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44798</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45316</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45987</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45987</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45239</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45427</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>46163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>46162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>46163</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>46163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>46162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45219</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45195</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45999</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45022</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>46000</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46001</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46000</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45623</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>46006</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>46008</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45764</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>46008</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45232</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46168</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45440</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>46168</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45007</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45493</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45698</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45756</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44746</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44525</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45567</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45176</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45784</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45009</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46043</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46042</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>46175</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46053</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45590</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>46178</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>46178</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46178</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>46178</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44592</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45363</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>46063</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>46063</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>44874</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46182</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45534</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>46185</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44460</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45238</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>46185</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45572</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46196</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45098</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45450</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45643</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44522</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45176</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45237</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>46121</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44523</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45764</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45533</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45236</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45541</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>44960</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45572</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45583</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45082</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45303</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44902</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45162</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45372</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45758</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45742</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>46251</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46251</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>46252</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>46252</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>46252</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44608</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>44942</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45572</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45643</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44823</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45715</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46214</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46214</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44861</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46219</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45758</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>45642</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45642</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>46224</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46224</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44907</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45845</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46268</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45776</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46269</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46272</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46272</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45764</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45490</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46272</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45420</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45764</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45614</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>46272</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>46272</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45764</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45764</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46274</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>46274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45145</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>46275</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>46274</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45589</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45642</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45533</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46234</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46276</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46276</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45533</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45614</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>46281</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>46237</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45462</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45643</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>45478</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45534</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>45517</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45588</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>44876</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45343</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46240</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45733</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>46239</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45533</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45621</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46283</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45692</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45691</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>45755</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>46283</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46239</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>44817</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45821</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45821</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45845</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45845</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>45845</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45845</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45755</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44616</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45523</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45145</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45731</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45692</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>43973</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>43973</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45383</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45383</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45034</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45209</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45383</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45716</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45733</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>46036</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46079</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46079</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>46079</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46014</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44476</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>44909</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>46204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45755</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>46100</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45755</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>45750</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>46154</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45916</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>45694</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>46141</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>46141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45548</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45231</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>45427</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>46125</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>46125</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45692</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>46141</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>46154</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>46163</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>46163</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>46175</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>46175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45478</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>46224</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45195</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44817</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45663</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45623</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>46141</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44699</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44795</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44862</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44819</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44714</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44871</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44812</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>44616</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44887</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>44810</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>44750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44708</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44762</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44782</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45232</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44804</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45755</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44798</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45238</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45533</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44832</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44806</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45692</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45691</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45572</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45450</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>44825</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45621</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45201</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45343</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45572</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45755</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45334</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45733</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44923</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45481</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45691</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45635</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45176</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44924</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45316</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>46043</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>44515</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>46053</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45007</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46063</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>46063</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45027</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45572</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44874</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45145</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>45399</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45936</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45372</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>44907</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45548</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45946</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44746</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45238</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45954</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45954</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45959</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45730</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45959</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45959</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45623</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45303</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45961</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45624</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45009</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>46121</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44867</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45642</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45022</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45698</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45427</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46136</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45681</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45987</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45987</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45567</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44756</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>46000</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45755</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45483</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>46000</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45763</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45055</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46001</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45534</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45839</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45932</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>46006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46008</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46008</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44817</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45176</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45845</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45821</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45821</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45769</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45845</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45077</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>44525</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45715</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45715</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>46141</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>46142</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45082</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>46149</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>46149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46153</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44792</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45932</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46148</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44868</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45363</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44930</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45758</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>44543</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45450</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>46162</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44907</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>46162</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>46163</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45845</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45845</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>46163</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>46163</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45755</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>46168</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>46168</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45237</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45523</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44657</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45980</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45784</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45756</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45567</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45145</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45544</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45493</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>44608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>46178</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45551</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45098</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>46183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45162</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45692</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>46182</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44613</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>46185</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45731</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45440</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45643</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>46196</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45162</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45710</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>46251</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>46251</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>46252</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>46252</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>46251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45642</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46252</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44613</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45623</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45666</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>46214</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46214</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45195</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45642</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45572</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>44749</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45643</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>46219</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45239</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45764</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>44861</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45236</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44754</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45764</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46268</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46224</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46224</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45217</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46269</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45845</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46272</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>46272</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>46272</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46272</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>46274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>44525</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>46274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45309</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44560</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>46276</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>46276</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46275</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45201</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45007</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>46234</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>46237</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>46281</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>46239</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46240</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>46283</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>46283</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>46283</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44954</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44496</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45764</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45572</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45493</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45372</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45572</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45572</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45201</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44942</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44852</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44902</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44663</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45643</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45068</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>45238</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>44592</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45187</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45590</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45412</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45335</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45541</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45715</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45763</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45742</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45583</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>45776</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45490</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45420</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45614</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45145</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45589</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45642</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45533</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45588</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45462</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45533</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45534</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45478</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45517</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>44876</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45643</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>43973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>43973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45383</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45383</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45383</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45733</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46036</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>46079</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>46014</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>46272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>44476</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>44909</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8064-2026</t>
+          <t>A 29741-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46063</v>
+        <v>46204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,17 +1916,22 @@
           <t>HÄLLEFORS</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1941,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1950,12 +1955,125 @@
         <v>5</v>
       </c>
       <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Nötkråka
+Plattlummer
+Mattlummer
+Skogsstjärna
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/artfynd/A 29741-2026 artfynd.xlsx", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor/A 29741-2026 karta.png", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor_geotiff/A 29741-2026 georefererad karta.tif", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomål/A 29741-2026 FSC-klagomål.docx", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomålsmail/A 29741-2026 FSC-klagomål mail.docx", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsyn/A 29741-2026 tillsynsbegäran.docx", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsynsmail/A 29741-2026 tillsynsbegäran mail.docx", "A 29741-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1863/fåglar/A 29741-2026 prioriterade fågelarter.docx", "A 29741-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 8064-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HÄLLEFORS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
         <v>9</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>9</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Ullticka
@@ -1964,111 +2082,111 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/artfynd/A 8064-2026 artfynd.xlsx", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor/A 8064-2026 karta.png", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor_geotiff/A 8064-2026 georefererad karta.tif", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomål/A 8064-2026 FSC-klagomål.docx", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomålsmail/A 8064-2026 FSC-klagomål mail.docx", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsyn/A 8064-2026 tillsynsbegäran.docx", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsynsmail/A 8064-2026 tillsynsbegäran mail.docx", "A 8064-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/fåglar/A 8064-2026 prioriterade fågelarter.docx", "A 8064-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 4652-2023</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>44957</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HÄLLEFORS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÄLLEFORS</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>2.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Vedtrappmossa
 Svart trolldruva
@@ -2076,153 +2194,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/artfynd/A 4652-2023 artfynd.xlsx", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor/A 4652-2023 karta.png", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor_geotiff/A 4652-2023 georefererad karta.tif", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomål/A 4652-2023 FSC-klagomål.docx", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomålsmail/A 4652-2023 FSC-klagomål mail.docx", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsyn/A 4652-2023 tillsynsbegäran.docx", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsynsmail/A 4652-2023 tillsynsbegäran mail.docx", "A 4652-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1863/fåglar/A 4652-2023 prioriterade fågelarter.docx", "A 4652-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 29741-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÄLLEFORS</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Mattlummer
-Skogsstjärna
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/artfynd/A 29741-2026 artfynd.xlsx", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor/A 29741-2026 karta.png", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/kartor_geotiff/A 29741-2026 georefererad karta.tif", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomål/A 29741-2026 FSC-klagomål.docx", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/klagomålsmail/A 29741-2026 FSC-klagomål mail.docx", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsyn/A 29741-2026 tillsynsbegäran.docx", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/tillsynsmail/A 29741-2026 tillsynsbegäran mail.docx", "A 29741-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1863/fåglar/A 29741-2026 prioriterade fågelarter.docx", "A 29741-2026")</f>
         <v/>
       </c>
     </row>
@@ -2246,7 +2247,7 @@
         <v>45755</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2358,7 +2359,7 @@
         <v>46100</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2475,7 @@
         <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2590,7 +2591,7 @@
         <v>45755</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2702,7 +2703,7 @@
         <v>45750</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2818,7 +2819,7 @@
         <v>46154</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2934,7 +2935,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3045,7 +3046,7 @@
         <v>45540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3161,7 @@
         <v>45916</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3272,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3386,7 +3387,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3501,7 +3502,7 @@
         <v>45694</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3612,7 +3613,7 @@
         <v>46141</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3723,7 +3724,7 @@
         <v>46141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3838,7 +3839,7 @@
         <v>46154</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3953,7 +3954,7 @@
         <v>46163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4064,7 +4065,7 @@
         <v>45845</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4175,7 +4176,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4281,7 +4282,7 @@
         <v>45548</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4388,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4498,7 +4499,7 @@
         <v>45989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4613,7 +4614,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4718,7 +4719,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4827,7 +4828,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4936,7 +4937,7 @@
         <v>45231</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5042,7 @@
         <v>45427</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5147,7 @@
         <v>46125</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5256,7 +5257,7 @@
         <v>46125</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5366,7 +5367,7 @@
         <v>45692</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5476,7 +5477,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5586,7 +5587,7 @@
         <v>46141</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5696,7 +5697,7 @@
         <v>46154</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5806,7 +5807,7 @@
         <v>46154</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5916,7 +5917,7 @@
         <v>46163</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6030,7 +6031,7 @@
         <v>46163</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6140,7 +6141,7 @@
         <v>45756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6254,7 +6255,7 @@
         <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6359,7 +6360,7 @@
         <v>46175</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6469,7 +6470,7 @@
         <v>46175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6579,7 +6580,7 @@
         <v>45478</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6689,7 +6690,7 @@
         <v>46190</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6794,7 +6795,7 @@
         <v>46224</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6904,7 +6905,7 @@
         <v>45195</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7009,7 +7010,7 @@
         <v>44817</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7114,7 +7115,7 @@
         <v>45663</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7224,7 +7225,7 @@
         <v>45623</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7335,7 @@
         <v>44671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7444,7 +7445,7 @@
         <v>46141</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7554,7 +7555,7 @@
         <v>44699</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7627,7 +7628,7 @@
         <v>44795</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7700,7 +7701,7 @@
         <v>44862</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7778,7 +7779,7 @@
         <v>44819</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7856,7 +7857,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7929,7 +7930,7 @@
         <v>44719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8002,7 +8003,7 @@
         <v>44792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8075,7 +8076,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8148,7 +8149,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8226,7 +8227,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8304,7 +8305,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8377,7 +8378,7 @@
         <v>44714</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8450,7 +8451,7 @@
         <v>44871</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8523,7 +8524,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8596,7 +8597,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8674,7 +8675,7 @@
         <v>44792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8752,7 +8753,7 @@
         <v>44812</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8825,7 +8826,7 @@
         <v>44616</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8898,7 +8899,7 @@
         <v>44887</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8976,7 +8977,7 @@
         <v>44810</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9049,7 +9050,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9122,7 +9123,7 @@
         <v>44750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9200,7 +9201,7 @@
         <v>44754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9278,7 +9279,7 @@
         <v>44754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9356,7 +9357,7 @@
         <v>44590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9429,7 +9430,7 @@
         <v>44817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9502,7 +9503,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9580,7 +9581,7 @@
         <v>44708</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9653,7 +9654,7 @@
         <v>44762</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9726,7 +9727,7 @@
         <v>44782</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9799,7 +9800,7 @@
         <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9877,7 +9878,7 @@
         <v>45232</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9955,7 +9956,7 @@
         <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10028,7 +10029,7 @@
         <v>44804</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10101,7 +10102,7 @@
         <v>45755</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10179,7 +10180,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10252,7 +10253,7 @@
         <v>44798</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10330,7 +10331,7 @@
         <v>45238</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10408,7 +10409,7 @@
         <v>45533</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10486,7 +10487,7 @@
         <v>44832</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10559,7 +10560,7 @@
         <v>44806</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10637,7 +10638,7 @@
         <v>45692</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10715,7 +10716,7 @@
         <v>45533</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10793,7 +10794,7 @@
         <v>45691</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10871,7 +10872,7 @@
         <v>45572</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10949,7 +10950,7 @@
         <v>45450</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11022,7 +11023,7 @@
         <v>44825</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11100,7 +11101,7 @@
         <v>45621</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11178,7 +11179,7 @@
         <v>45201</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11256,7 +11257,7 @@
         <v>45343</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11329,7 +11330,7 @@
         <v>45572</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11407,7 +11408,7 @@
         <v>45755</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11485,7 +11486,7 @@
         <v>45334</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11558,7 +11559,7 @@
         <v>45733</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11636,7 +11637,7 @@
         <v>44923</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11709,7 +11710,7 @@
         <v>45481</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11782,7 +11783,7 @@
         <v>45691</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11860,7 +11861,7 @@
         <v>45635</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11933,7 +11934,7 @@
         <v>45176</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12011,7 +12012,7 @@
         <v>45755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12089,7 +12090,7 @@
         <v>44924</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12162,7 +12163,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12240,7 +12241,7 @@
         <v>45316</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12318,7 +12319,7 @@
         <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12391,7 +12392,7 @@
         <v>46043</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12464,7 +12465,7 @@
         <v>44515</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12542,7 +12543,7 @@
         <v>46053</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12615,7 +12616,7 @@
         <v>45007</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12693,7 +12694,7 @@
         <v>44960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12772,7 @@
         <v>46063</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12844,7 +12845,7 @@
         <v>46063</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12917,7 +12918,7 @@
         <v>45027</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12995,7 +12996,7 @@
         <v>45572</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13073,7 +13074,7 @@
         <v>44874</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13151,7 +13152,7 @@
         <v>45145</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13229,7 +13230,7 @@
         <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13307,7 +13308,7 @@
         <v>45399</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13385,7 +13386,7 @@
         <v>45936</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13458,7 +13459,7 @@
         <v>45372</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13531,7 +13532,7 @@
         <v>44907</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13609,7 +13610,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13682,7 +13683,7 @@
         <v>45548</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13755,7 +13756,7 @@
         <v>45946</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13833,7 +13834,7 @@
         <v>45946</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13911,7 +13912,7 @@
         <v>45946</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13989,7 +13990,7 @@
         <v>44746</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14062,7 +14063,7 @@
         <v>45238</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14135,7 +14136,7 @@
         <v>45954</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14213,7 +14214,7 @@
         <v>45954</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14291,7 +14292,7 @@
         <v>45959</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14364,7 +14365,7 @@
         <v>45730</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14437,7 +14438,7 @@
         <v>45959</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14510,7 +14511,7 @@
         <v>45959</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14583,7 +14584,7 @@
         <v>45623</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14661,7 +14662,7 @@
         <v>45303</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14734,7 +14735,7 @@
         <v>45961</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14807,7 +14808,7 @@
         <v>45624</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14885,7 +14886,7 @@
         <v>45009</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14963,7 +14964,7 @@
         <v>46121</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15036,7 +15037,7 @@
         <v>44867</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15114,7 +15115,7 @@
         <v>45642</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15192,7 +15193,7 @@
         <v>45022</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15265,7 +15266,7 @@
         <v>45000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15343,7 +15344,7 @@
         <v>45698</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15421,7 +15422,7 @@
         <v>45427</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15494,7 +15495,7 @@
         <v>46136</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15572,7 +15573,7 @@
         <v>45681</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15645,7 +15646,7 @@
         <v>45987</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15723,7 +15724,7 @@
         <v>45987</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15801,7 +15802,7 @@
         <v>45567</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15879,7 +15880,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15957,7 +15958,7 @@
         <v>44756</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16035,7 +16036,7 @@
         <v>46000</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16113,7 +16114,7 @@
         <v>45755</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16191,7 +16192,7 @@
         <v>45483</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16264,7 +16265,7 @@
         <v>46000</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16342,7 +16343,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16420,7 +16421,7 @@
         <v>45763</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16498,7 +16499,7 @@
         <v>45055</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16571,7 +16572,7 @@
         <v>46001</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16649,7 +16650,7 @@
         <v>45534</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16727,7 +16728,7 @@
         <v>45839</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16800,7 +16801,7 @@
         <v>45932</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16878,7 +16879,7 @@
         <v>46006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16951,7 +16952,7 @@
         <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17029,7 +17030,7 @@
         <v>46008</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17102,7 +17103,7 @@
         <v>46008</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17175,7 +17176,7 @@
         <v>45845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17253,7 +17254,7 @@
         <v>45601</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17331,7 +17332,7 @@
         <v>44817</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17409,7 +17410,7 @@
         <v>45176</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17487,7 +17488,7 @@
         <v>45987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17565,7 +17566,7 @@
         <v>45987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17643,7 +17644,7 @@
         <v>45845</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17721,7 +17722,7 @@
         <v>45821</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17794,7 +17795,7 @@
         <v>45821</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17867,7 +17868,7 @@
         <v>45769</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17945,7 +17946,7 @@
         <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18023,7 +18024,7 @@
         <v>45845</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18101,7 +18102,7 @@
         <v>45077</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18179,7 +18180,7 @@
         <v>44525</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18252,7 +18253,7 @@
         <v>45715</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18325,7 +18326,7 @@
         <v>45715</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18398,7 +18399,7 @@
         <v>46141</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18476,7 +18477,7 @@
         <v>46142</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18549,7 +18550,7 @@
         <v>45082</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18627,7 +18628,7 @@
         <v>46149</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18700,7 +18701,7 @@
         <v>46149</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18773,7 +18774,7 @@
         <v>46153</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18851,7 +18852,7 @@
         <v>44792</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18924,7 +18925,7 @@
         <v>45932</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19002,7 +19003,7 @@
         <v>46148</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19080,7 +19081,7 @@
         <v>44868</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19158,7 +19159,7 @@
         <v>45363</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19236,7 +19237,7 @@
         <v>44930</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19309,7 +19310,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19387,7 +19388,7 @@
         <v>45758</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19460,7 +19461,7 @@
         <v>44543</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19538,7 +19539,7 @@
         <v>45450</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19611,7 +19612,7 @@
         <v>46162</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19684,7 +19685,7 @@
         <v>44907</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19762,7 +19763,7 @@
         <v>46162</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19835,7 +19836,7 @@
         <v>45845</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19908,7 +19909,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19986,7 +19987,7 @@
         <v>46163</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20064,7 +20065,7 @@
         <v>45845</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20142,7 +20143,7 @@
         <v>45845</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20220,7 +20221,7 @@
         <v>46163</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20298,7 +20299,7 @@
         <v>46163</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20376,7 +20377,7 @@
         <v>45755</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20454,7 +20455,7 @@
         <v>44616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20527,7 +20528,7 @@
         <v>46168</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20600,7 +20601,7 @@
         <v>46168</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20673,7 +20674,7 @@
         <v>45237</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20751,7 +20752,7 @@
         <v>45523</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20824,7 +20825,7 @@
         <v>44657</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20897,7 +20898,7 @@
         <v>45980</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20970,7 +20971,7 @@
         <v>45784</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21043,7 +21044,7 @@
         <v>45756</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21116,7 +21117,7 @@
         <v>45567</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21194,7 +21195,7 @@
         <v>45145</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21272,7 +21273,7 @@
         <v>46175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21345,7 +21346,7 @@
         <v>45544</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21418,7 +21419,7 @@
         <v>45493</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21491,7 +21492,7 @@
         <v>44608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21564,7 +21565,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21642,7 +21643,7 @@
         <v>46178</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21720,7 +21721,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21798,7 +21799,7 @@
         <v>45551</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21871,7 +21872,7 @@
         <v>45098</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21944,7 +21945,7 @@
         <v>46183</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22017,7 +22018,7 @@
         <v>45162</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22095,7 +22096,7 @@
         <v>45692</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22173,7 +22174,7 @@
         <v>46182</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22251,7 +22252,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22329,7 +22330,7 @@
         <v>44613</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22407,7 +22408,7 @@
         <v>46185</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22480,7 +22481,7 @@
         <v>45731</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22553,7 +22554,7 @@
         <v>45440</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22626,7 +22627,7 @@
         <v>45643</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22704,7 +22705,7 @@
         <v>46196</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22782,7 +22783,7 @@
         <v>45162</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22860,7 +22861,7 @@
         <v>45710</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22933,7 +22934,7 @@
         <v>46251</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23011,7 +23012,7 @@
         <v>46251</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23089,7 +23090,7 @@
         <v>46252</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23167,7 +23168,7 @@
         <v>46252</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23245,7 +23246,7 @@
         <v>46251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23323,7 +23324,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23401,7 +23402,7 @@
         <v>45642</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23479,7 +23480,7 @@
         <v>46252</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23557,7 +23558,7 @@
         <v>44613</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23635,7 +23636,7 @@
         <v>45623</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23713,7 +23714,7 @@
         <v>45666</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23786,7 +23787,7 @@
         <v>45434</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23859,7 +23860,7 @@
         <v>46214</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23937,7 +23938,7 @@
         <v>46214</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24015,7 +24016,7 @@
         <v>45195</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24088,7 +24089,7 @@
         <v>45642</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24166,7 +24167,7 @@
         <v>45572</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24239,7 +24240,7 @@
         <v>44749</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24312,7 +24313,7 @@
         <v>45643</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24390,7 +24391,7 @@
         <v>46219</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24463,7 +24464,7 @@
         <v>45239</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24536,7 +24537,7 @@
         <v>45764</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24614,7 +24615,7 @@
         <v>44861</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24692,7 +24693,7 @@
         <v>45236</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24765,7 +24766,7 @@
         <v>44754</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24843,7 +24844,7 @@
         <v>45764</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24916,7 +24917,7 @@
         <v>46268</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24989,7 +24990,7 @@
         <v>46224</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25067,7 +25068,7 @@
         <v>46224</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25145,7 +25146,7 @@
         <v>45217</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25223,7 +25224,7 @@
         <v>46269</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25296,7 +25297,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25374,7 +25375,7 @@
         <v>45845</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25447,7 +25448,7 @@
         <v>46272</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25525,7 +25526,7 @@
         <v>46272</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25603,7 +25604,7 @@
         <v>46272</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25681,7 +25682,7 @@
         <v>46272</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25759,7 +25760,7 @@
         <v>46274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25837,7 +25838,7 @@
         <v>44525</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25915,7 +25916,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25993,7 +25994,7 @@
         <v>46274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26071,7 +26072,7 @@
         <v>45309</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26144,7 +26145,7 @@
         <v>44560</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26222,7 +26223,7 @@
         <v>46276</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26300,7 +26301,7 @@
         <v>46276</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26378,7 +26379,7 @@
         <v>46275</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26451,7 +26452,7 @@
         <v>45201</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26529,7 +26530,7 @@
         <v>45007</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26607,7 +26608,7 @@
         <v>46234</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26685,7 +26686,7 @@
         <v>46237</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26763,7 +26764,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26841,7 +26842,7 @@
         <v>46281</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26919,7 +26920,7 @@
         <v>46239</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26997,7 +26998,7 @@
         <v>46240</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27075,7 +27076,7 @@
         <v>46283</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27153,7 +27154,7 @@
         <v>46283</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27231,7 +27232,7 @@
         <v>46283</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27309,7 +27310,7 @@
         <v>44954</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27382,7 +27383,7 @@
         <v>44522</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27455,7 +27456,7 @@
         <v>44979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27528,7 +27529,7 @@
         <v>44496</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27601,7 +27602,7 @@
         <v>45764</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27674,7 +27675,7 @@
         <v>45572</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27752,7 +27753,7 @@
         <v>45493</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27825,7 +27826,7 @@
         <v>45372</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27898,7 +27899,7 @@
         <v>45572</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27971,7 +27972,7 @@
         <v>45572</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28044,7 +28045,7 @@
         <v>45201</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28117,7 +28118,7 @@
         <v>44942</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28190,7 +28191,7 @@
         <v>44852</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28268,7 +28269,7 @@
         <v>44902</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28346,7 +28347,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28424,7 +28425,7 @@
         <v>44663</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28502,7 +28503,7 @@
         <v>45643</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28580,7 +28581,7 @@
         <v>45068</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28653,7 +28654,7 @@
         <v>45238</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28726,7 +28727,7 @@
         <v>44592</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28799,7 +28800,7 @@
         <v>45187</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28872,7 +28873,7 @@
         <v>45590</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28950,7 +28951,7 @@
         <v>45412</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29023,7 +29024,7 @@
         <v>45335</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29096,7 +29097,7 @@
         <v>45541</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29169,7 +29170,7 @@
         <v>45715</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29242,7 +29243,7 @@
         <v>45763</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29320,7 +29321,7 @@
         <v>45742</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29393,7 +29394,7 @@
         <v>45583</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29471,7 +29472,7 @@
         <v>45776</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29549,7 +29550,7 @@
         <v>45490</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29622,7 +29623,7 @@
         <v>45420</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29695,7 +29696,7 @@
         <v>45614</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29768,7 +29769,7 @@
         <v>45145</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29846,7 +29847,7 @@
         <v>45589</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29924,7 +29925,7 @@
         <v>45642</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30002,7 +30003,7 @@
         <v>45533</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30080,7 +30081,7 @@
         <v>45588</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30158,7 +30159,7 @@
         <v>45462</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30236,7 +30237,7 @@
         <v>45533</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30314,7 +30315,7 @@
         <v>45534</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30392,7 +30393,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30465,7 +30466,7 @@
         <v>45478</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30543,7 +30544,7 @@
         <v>45517</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30621,7 +30622,7 @@
         <v>44876</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30699,7 +30700,7 @@
         <v>45643</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30777,7 +30778,7 @@
         <v>45036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30855,7 +30856,7 @@
         <v>43973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30933,7 +30934,7 @@
         <v>43973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31011,7 +31012,7 @@
         <v>45383</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31084,7 +31085,7 @@
         <v>45383</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31157,7 +31158,7 @@
         <v>45034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31235,7 +31236,7 @@
         <v>45209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31313,7 +31314,7 @@
         <v>45383</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31386,7 +31387,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31464,7 +31465,7 @@
         <v>45733</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31537,7 +31538,7 @@
         <v>46036</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31615,7 +31616,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31688,7 +31689,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31761,7 +31762,7 @@
         <v>46079</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31834,7 +31835,7 @@
         <v>46014</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31912,7 +31913,7 @@
         <v>46272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>44476</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44909</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>46204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>46063</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46125</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45750</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45755</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46108</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45989</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>46141</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45663</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45478</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45427</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46125</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>46125</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45692</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45756</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45755</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>46141</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46154</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>46163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45980</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>46175</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>46175</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46224</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45195</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>46141</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44699</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44795</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44862</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44819</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44714</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44871</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44812</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44616</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44887</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44810</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44590</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44817</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44754</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44708</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44762</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44782</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44907</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45624</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45572</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45335</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45007</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45238</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>45201</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>45462</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45643</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>46006</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46008</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45027</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45483</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45691</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45534</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44806</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45755</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45588</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45544</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45145</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45450</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>46043</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>46042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45343</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>46044</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45572</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45533</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45621</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45692</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45755</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>44825</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44754</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>46053</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45681</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44657</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>44924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44525</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45730</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45936</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45037</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44515</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45187</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45217</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45162</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45946</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45946</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44867</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44832</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44954</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45412</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45642</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44817</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45954</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45959</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45961</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45959</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45715</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45434</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44663</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45635</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45219</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44923</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45821</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>44496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45068</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45821</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45987</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45987</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>46121</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44756</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>46000</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45309</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>46001</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44868</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45710</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45845</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45932</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>45987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45845</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45845</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45845</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45601</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44979</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>45755</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45334</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44616</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45845</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45839</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45845</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44852</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>46136</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45567</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45763</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45523</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45399</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45201</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45845</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45666</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45623</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45548</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45238</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45769</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45145</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>46141</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45731</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>46142</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44930</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45643</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>46149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>46149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45692</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44613</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45932</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>46153</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>44613</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>46148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45372</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>46163</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46163</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45493</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45201</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46162</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46168</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>46168</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45316</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45239</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45980</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45567</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>45784</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45427</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>46178</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>46178</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45201</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45572</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>46182</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>46183</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45219</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45195</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46185</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45022</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46185</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45623</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45764</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>46196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45440</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45007</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45493</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45000</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45698</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>44525</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45009</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46214</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>46214</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45590</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46219</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44592</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45363</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46224</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>46224</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44874</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46268</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>46269</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45534</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>46272</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>46272</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>46272</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>46272</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44749</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45238</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46274</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>46275</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>46234</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46276</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>46276</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>46281</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>46237</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45572</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46240</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>46239</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46283</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>46283</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>46283</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46239</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45098</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45450</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45643</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44522</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45763</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45176</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45237</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45642</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44523</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45764</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>46293</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45533</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45236</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45541</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45572</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45583</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45082</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46252</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46252</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46251</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45303</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46252</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>44902</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45162</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45372</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45758</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45742</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44608</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44942</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45572</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45643</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44823</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45715</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45755</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44861</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45758</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45642</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45642</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44907</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45776</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45490</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45420</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45145</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45589</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45642</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45533</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>43973</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>43973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45036</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45383</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45383</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45383</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45733</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46036</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46079</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46014</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>46272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>44476</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44909</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>46204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>46063</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>44957</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>46125</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45750</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45755</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>44543</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45540</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45916</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46108</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45694</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45989</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45845</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>46141</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45989</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>44818</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45663</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45478</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45427</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>46125</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>46125</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45692</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45756</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45755</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>46141</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46154</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>46163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45980</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>46175</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>46175</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>46190</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>46224</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>45231</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45195</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>46141</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44699</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44795</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44862</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44819</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>44792</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44515</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44714</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44871</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44812</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44616</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44887</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44810</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44590</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44817</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44754</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44708</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44762</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44782</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>44907</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45624</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45572</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45335</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45007</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45533</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45238</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>45201</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>45462</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45643</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>46006</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46008</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>45478</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45027</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45483</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45691</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45534</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44543</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>45517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44806</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45755</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45588</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45544</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45145</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45450</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>46043</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>46042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45343</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>46044</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45572</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45533</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45621</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45692</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45691</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45755</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>44825</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44754</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>46053</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45681</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>44657</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>44924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>44525</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45730</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45936</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>45037</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44515</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45187</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45217</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45162</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45946</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>45946</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>44867</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44832</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44954</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45412</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45642</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44817</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45954</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45954</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45959</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45961</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45959</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45715</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45434</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44663</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45635</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45219</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44923</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45821</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>44496</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45068</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45821</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45987</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45987</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>46121</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44756</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45999</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>46000</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45309</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>46001</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45077</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44868</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45710</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45845</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45932</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45987</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>45987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45845</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45845</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45845</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45601</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44979</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>45755</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45334</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44616</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45845</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45839</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45845</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44852</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>46136</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45567</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45763</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45523</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45399</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45201</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45845</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45666</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45623</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45548</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45238</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45769</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45145</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>46141</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45731</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>46142</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44930</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45643</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>46149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>46149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45692</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44613</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45932</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>46153</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>44613</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>46148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45372</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>46163</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46163</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46163</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45493</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45201</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46162</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44798</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46168</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>46168</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45316</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45239</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45980</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45567</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>45784</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45427</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>46178</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>46178</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45201</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45572</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>46182</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>46183</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45219</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45195</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>46185</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45022</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46185</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45623</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45764</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>46196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45440</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45007</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45493</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45000</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45698</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>44525</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45009</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46214</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>46214</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45590</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46219</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44592</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45363</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46224</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>46224</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44874</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46268</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>46269</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45534</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>46272</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>46272</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>46272</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>46272</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44749</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45238</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46274</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>46275</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>46234</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46276</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>46276</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>46281</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>46237</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45572</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46240</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>46239</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46283</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>46283</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>46283</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46239</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45098</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45450</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45643</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44522</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45763</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45176</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45237</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45642</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44523</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45764</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>46293</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45533</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>45236</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45541</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45572</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45583</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45082</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46252</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46252</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>46251</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28658,7 +28658,7 @@
         <v>46251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45303</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46252</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>44902</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45162</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45372</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45758</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45742</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44608</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44942</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45572</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45643</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44823</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45715</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45755</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44861</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45758</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45642</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45642</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44907</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45776</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45490</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45420</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45614</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45145</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45589</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45642</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45533</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>43973</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>43973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45036</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45383</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45383</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45034</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45209</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45383</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45733</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46036</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46079</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46014</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>46272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45755</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46125</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45750</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>44543</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45916</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45845</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45694</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>46108</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45989</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45548</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46141</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45231</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45195</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45663</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45623</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45427</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45756</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46125</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>46125</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>45692</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45755</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>46141</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>46154</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>46175</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>46175</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>46224</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44795</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44525</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44616</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44721</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44750</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44590</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44871</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>44887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45232</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44762</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>44782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44804</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44792</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45238</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44832</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44902</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44868</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45363</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45201</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45037</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44543</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>44663</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45450</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45755</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45643</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44823</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45068</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44798</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44907</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45238</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45533</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45187</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45590</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45412</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44806</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45201</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44657</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45450</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44825</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45334</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44923</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45335</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45541</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45481</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45635</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45176</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45715</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45493</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45316</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45763</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44608</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45742</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45551</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45583</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44515</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45490</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45420</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45162</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44613</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45145</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45589</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45007</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44960</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45642</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45533</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45588</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45462</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45440</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45534</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45614</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45027</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45643</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45572</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45478</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45517</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44876</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44874</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45643</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45692</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45691</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45621</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45343</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45572</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45755</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45399</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45733</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45710</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44907</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44523</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45936</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>44817</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44746</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44613</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45623</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45666</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45730</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45434</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45623</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45303</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45821</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45821</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45624</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45195</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45642</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45572</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44867</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44749</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45643</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45954</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45954</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45959</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45959</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45642</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45961</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45022</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45764</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>44861</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45427</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45845</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45236</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45845</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45681</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45845</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45845</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44616</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44754</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45764</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44756</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45523</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45483</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45217</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45145</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45055</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45534</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45692</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45731</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44525</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44817</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45176</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45309</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>44560</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45758</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45201</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45007</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45077</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44525</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45715</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45715</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45987</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45082</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>46121</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>46000</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>46000</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46001</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44522</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46006</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44979</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>46136</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46008</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46008</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45567</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45932</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45572</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45763</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45839</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45932</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45493</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45372</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45764</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45845</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45601</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45987</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45987</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45845</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45572</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46044</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45572</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45201</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46043</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45769</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45845</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44942</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44852</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>46141</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>46053</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>46142</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>46063</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46063</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>46149</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>46149</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>46153</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45932</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46148</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46162</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46163</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46163</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>46168</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46168</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45784</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45756</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45567</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>46175</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>46178</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>46178</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>46178</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>46183</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46182</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>46185</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46196</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>46214</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46219</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46268</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>46224</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46224</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>46272</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>46272</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>46272</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>46272</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46272</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46274</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>46274</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46276</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>46276</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>46275</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>46234</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46237</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46281</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>46239</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46240</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46283</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46283</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46283</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45764</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46251</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46251</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46252</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>46251</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46301</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>46293</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46301</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46302</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45946</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45036</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>43973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>43973</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45383</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45383</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45034</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45209</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45383</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45716</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45733</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46079</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46079</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46014</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46272</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>46252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45755</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>46100</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46125</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45750</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>44543</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45540</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45916</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45845</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45694</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>46108</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45989</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45548</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>46141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46141</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45231</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45195</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45663</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45623</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>45427</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45756</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>46125</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>46125</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>45692</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45755</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>46141</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>46154</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>46154</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>45980</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>46175</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>46175</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>46190</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>46224</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44795</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44792</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44525</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44616</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44721</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44750</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44515</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44590</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44871</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>44887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45232</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44762</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>44782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44804</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44792</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45238</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44832</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44902</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45219</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44868</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45363</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45201</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45037</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44543</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>44663</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45450</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45755</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45643</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44823</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45068</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44798</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44907</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45238</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44592</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45533</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45187</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45590</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45412</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44806</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45201</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44657</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45450</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44825</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45691</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45334</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44923</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45335</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45541</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45481</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45635</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45176</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45715</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45493</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45316</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45763</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44608</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45742</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45551</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45583</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44515</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45098</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45490</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45420</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45162</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44613</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45145</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45589</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45007</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44960</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45642</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45533</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45588</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45462</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45533</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45440</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45534</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45614</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45027</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45643</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45572</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45478</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45517</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44876</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44874</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45643</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45692</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45691</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45621</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45343</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45572</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45755</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45399</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45733</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45710</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>44907</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44523</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45936</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>44817</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45642</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44746</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44613</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45623</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45666</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45730</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45434</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45623</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45303</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45821</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45821</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45624</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45195</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45642</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45572</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44867</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44749</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45643</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45954</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45954</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45959</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45959</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45642</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45961</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45022</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45764</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>44861</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45427</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45845</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45236</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45845</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>45681</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45845</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45845</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45755</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44616</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44754</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45764</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44756</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45523</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45483</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45217</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45145</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45055</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45534</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45692</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45731</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44525</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44817</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45176</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45309</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>44560</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45758</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45201</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45007</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45077</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44525</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45715</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45715</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45987</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45082</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>46121</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>46000</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>46000</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46001</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44522</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46006</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44979</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>46136</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46008</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46008</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45567</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45932</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45572</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45763</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45839</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45932</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45493</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45372</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45764</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45845</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45601</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45987</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45987</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45845</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45572</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46044</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45572</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45201</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46043</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45769</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45845</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44942</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44852</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>46141</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>46053</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>46142</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>46063</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46063</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>46149</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>46149</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>46153</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45932</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46148</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46162</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46163</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46163</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>46168</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46168</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45784</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45756</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45567</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>46175</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>46178</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>46178</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>46178</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>46183</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46182</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>46185</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46196</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>46214</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46219</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46268</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>46224</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46224</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>46272</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>46272</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>46272</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>46272</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46272</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46274</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>46274</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46276</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>46276</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>46275</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>46234</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46237</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46281</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>46239</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46240</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46283</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46283</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46283</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45764</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>46251</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>46251</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>46252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>46252</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>46251</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>46301</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>46293</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46301</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>46302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46302</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45946</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45036</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>43973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>43973</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45383</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45383</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45034</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45209</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45383</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45716</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45733</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46036</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46079</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46079</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46014</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46272</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>46252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>44909</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45750</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45755</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46154</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>44543</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45548</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44594</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46141</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45916</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>46163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45989</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>46108</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45427</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45755</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>46141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>46154</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>46175</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>46175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>46125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>46125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45692</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>46224</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45231</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45195</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44817</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45663</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44795</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44714</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44871</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44812</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44616</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44810</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44590</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>44754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44907</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45624</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45572</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44560</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45335</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45007</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>45238</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45201</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45027</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45483</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>44543</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44806</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45145</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45450</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45572</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44825</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44754</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>44924</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44657</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44525</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>45681</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45730</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45037</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45187</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44515</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45217</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45162</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44867</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45412</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45642</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44817</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45434</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45715</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44663</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44923</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45551</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45068</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45932</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45764</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45481</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45845</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45839</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45845</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>46136</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44756</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45691</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45567</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45763</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45201</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45309</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45755</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44868</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45769</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46141</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45710</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>46142</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>46149</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44979</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45334</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46149</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44852</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>44792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45932</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45936</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45399</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45201</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45946</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45666</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45623</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45548</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45238</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46148</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45954</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45954</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45959</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45959</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45961</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45959</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>46163</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>46162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>46163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45643</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44613</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45755</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44613</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45372</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>46168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45493</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45201</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>44798</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46000</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46001</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46000</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45980</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45756</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46006</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45316</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45239</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>46008</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45567</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45427</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45572</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45219</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45022</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46175</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46178</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>46178</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46178</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>46043</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45623</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>46042</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45764</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46053</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45232</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>46183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>46063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45440</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45007</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45493</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46185</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45000</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45698</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44746</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44525</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45176</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45590</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>46196</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>44592</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45363</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>46121</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44874</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45534</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44749</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45238</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45572</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>46214</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45098</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>46219</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45450</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45643</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>44522</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45763</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46224</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>46224</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45176</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>46272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>46272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45237</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>46272</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46272</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>46272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>44523</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>46274</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>46274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45764</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>46275</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45533</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46274</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45236</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46234</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45541</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>44960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46276</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46276</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45082</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45303</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46237</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44902</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46240</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>46239</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46283</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46283</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45162</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46283</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45372</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>46239</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45758</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45742</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44608</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44942</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45572</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44823</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45715</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45764</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45755</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44861</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46252</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>46252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>46251</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>46251</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>46251</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>46252</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45758</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45642</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45642</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44907</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45776</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46301</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>46293</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>46301</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45490</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45420</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45614</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45145</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45589</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45642</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45533</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46302</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45533</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46302</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45614</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45462</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45643</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45478</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45534</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45517</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45588</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>44876</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45343</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45533</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45572</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45621</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45692</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45691</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45755</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>44817</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46301</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46269</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45821</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>45821</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>46268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45845</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45845</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45845</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45845</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45755</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>44616</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45523</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45145</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45731</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45692</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>43973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>43973</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45036</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45383</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45383</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45034</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45209</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45383</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45716</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45733</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46036</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46079</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>46014</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46272</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46252</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>46100</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>44909</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>46204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45750</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>45755</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>46154</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>46125</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>44543</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45548</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44594</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45694</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46141</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>46141</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45916</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>46154</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>46163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45989</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>46108</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>45845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45427</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45755</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>46141</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>46154</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>46154</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>46175</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>46175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>46190</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>46125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>46125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45692</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>46224</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45231</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45195</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44817</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45663</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44795</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44714</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44871</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44812</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44616</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44810</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44590</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>44754</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44907</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45624</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45572</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>44560</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45335</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45007</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>45238</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45201</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45027</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45483</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>44543</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44806</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45145</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45450</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45572</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44825</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44754</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>44924</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44657</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44525</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>45681</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45730</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45037</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45187</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44515</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45217</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45162</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>44867</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45412</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45642</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44817</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45434</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45715</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44663</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45635</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44923</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45551</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45068</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45932</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45987</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45764</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45481</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45715</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45845</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45839</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45845</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>46136</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44756</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45691</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45567</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45763</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45201</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45309</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45755</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44868</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45769</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46141</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45710</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>46142</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>46149</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44979</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45334</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46149</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44852</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>44792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45932</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45936</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45399</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45201</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45946</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45666</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45623</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45548</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45238</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46148</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45954</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45954</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45959</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45959</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45961</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45959</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44930</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>46163</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>46162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>46163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45643</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44613</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45755</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44613</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45987</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45372</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>46168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45493</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45201</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>44798</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46000</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46001</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46000</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45980</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45756</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46006</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45316</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45239</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>46008</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45567</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45427</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45572</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45219</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45022</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46175</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46178</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>46178</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46178</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>46043</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45623</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>46042</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45764</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>46053</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45232</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>46183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>46063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45440</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45007</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45493</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46185</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45000</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45698</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44746</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44525</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45176</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45590</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>46196</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>44592</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45363</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>46121</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44874</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45534</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44749</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45238</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45572</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>46214</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45098</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>46219</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45450</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45643</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>44522</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45763</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46224</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>46224</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45176</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>46272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>46272</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45237</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>46272</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46272</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>46272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>44523</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>46274</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>46274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45764</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>46275</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45533</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46274</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45236</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46234</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45541</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>44960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46276</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46276</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45082</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45303</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46237</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44902</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46240</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>46239</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46283</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46283</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45162</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46283</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45372</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>46239</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45758</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45742</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44608</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44942</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45572</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44823</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45715</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45764</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45755</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44861</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46252</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>46252</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>46251</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>46251</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>46251</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>46252</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45758</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45642</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45642</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44907</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45776</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46301</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>46293</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>46301</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45490</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45420</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45614</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45145</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45589</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45642</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45533</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46302</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45533</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46302</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45614</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45462</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45643</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45478</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45534</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45517</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45588</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>44876</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>45343</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45533</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45572</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45621</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45692</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>45691</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45755</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>44817</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46301</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46269</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45821</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>45821</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>46268</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45845</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>45845</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45845</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45845</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45755</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>44616</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45523</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45145</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45731</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45692</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>43973</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>43973</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45036</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45383</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45383</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45034</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45209</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45383</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45716</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45733</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46036</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46079</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>46079</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>46014</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46272</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46252</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>46204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>46100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46125</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45755</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45750</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44543</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45540</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45916</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45176</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45845</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>46108</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45548</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>46163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>46175</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45231</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>46190</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45663</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45756</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>46125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>46125</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>45692</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>46154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45427</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45478</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44795</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44714</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44871</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44812</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44616</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44810</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44590</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44979</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44496</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45691</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45755</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45201</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>46162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45493</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>46163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45372</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>46163</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>46163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>46168</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46168</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45572</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45201</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45756</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>45219</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45567</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44942</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45238</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>44832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>46175</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45946</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>44823</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44798</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>46178</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>46178</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>46178</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44902</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45954</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45954</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45201</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46183</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>46182</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44663</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45643</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45959</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45068</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45959</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45959</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45238</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45961</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44592</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45187</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45590</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45412</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45335</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45541</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>44806</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46214</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46000</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45742</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45583</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45776</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>46224</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>46224</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45490</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45420</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>46008</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>46008</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45145</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45589</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>46234</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>46237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45462</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45533</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46239</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45534</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>46281</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45614</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>46239</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46240</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>45478</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>46283</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>46283</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>46283</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45517</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44876</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45572</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45643</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45692</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45533</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45691</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45621</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45343</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45572</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45755</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46044</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>46043</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45733</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45450</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>46053</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45764</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>46063</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>46063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45821</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>46251</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46252</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>46252</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>46252</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>46251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45334</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45845</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44923</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45845</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45845</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>46301</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>46293</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44616</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>46301</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46302</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45523</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45481</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>46302</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45145</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45635</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45176</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45692</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>46121</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>45731</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>44924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45316</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45946</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44515</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46136</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45567</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>46301</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45932</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45839</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46268</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45932</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>46269</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45764</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45027</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45572</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>46272</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45987</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45987</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45845</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>44874</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>46272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46272</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45769</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>46272</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45845</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45145</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>46315</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46315</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>46274</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>46276</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46276</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45399</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46141</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45372</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>46274</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>44907</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44523</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>46142</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45548</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>46275</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>46274</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>46149</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46149</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>46153</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44746</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45238</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>46148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45730</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45623</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45303</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45624</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45009</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44867</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45642</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45022</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45698</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45427</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>44756</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45755</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45483</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45534</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>44817</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45176</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45758</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45077</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44525</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45715</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45715</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45082</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44792</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44868</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45363</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45758</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44543</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45450</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44907</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45237</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44657</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45544</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45493</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44608</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45551</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45098</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45162</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44613</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45440</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45643</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45162</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45710</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45642</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45642</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44613</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45623</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45666</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45434</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45195</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45642</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>44749</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45764</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44861</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45236</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>44754</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45764</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45217</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44525</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45309</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44560</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45201</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>45007</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>44954</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44522</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45036</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>43973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>43973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45383</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45383</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45034</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45209</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45383</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45716</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45733</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46036</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46079</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46014</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>46272</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>

--- a/Översikt HÄLLEFORS.xlsx
+++ b/Översikt HÄLLEFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45628</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>45562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46204</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>45951</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45132</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44624</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44909</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46100</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>46204</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>46063</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>44957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>46100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46125</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45755</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45755</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45750</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44543</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>45540</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45916</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45176</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>45845</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>46108</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46141</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46141</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45694</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45548</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44818</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>46163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>46175</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45231</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>46190</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45663</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45756</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>46125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>46125</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>45692</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>46154</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>46154</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45427</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45478</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44795</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44792</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44721</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44714</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44871</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44858</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44812</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44616</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44810</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>44525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44590</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44979</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44496</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45691</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45755</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45201</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>46162</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>46162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45493</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>46163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45372</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>46163</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>46163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>46168</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46168</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45572</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45201</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45784</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45756</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>45219</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45567</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44942</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44852</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45238</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>44832</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>46175</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>45755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45946</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>44823</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44798</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>46178</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>46178</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>46178</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44902</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45954</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45954</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45201</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46183</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>46182</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44663</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45643</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45959</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45068</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45959</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45959</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45238</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45961</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44592</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45187</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45590</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45412</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45335</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45541</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>44806</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46214</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46000</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45742</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>45583</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>45776</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>46224</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>46224</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>46001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45490</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45420</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>46008</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>46008</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>45145</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45589</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>46234</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>46237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45462</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45533</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46239</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45534</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>46281</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45614</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>46239</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46240</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17004,7 +17004,7 @@
         <v>45478</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>46283</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>46283</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>46283</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>45517</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44876</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45572</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45643</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45692</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45533</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45691</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45621</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45343</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45572</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45755</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46044</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>46043</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45733</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45450</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>46053</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45764</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>46063</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>46063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45821</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>46251</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46252</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>46252</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>46252</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>46251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45334</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>45845</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44923</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45845</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45845</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>46301</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>46293</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45755</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44616</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>46301</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46302</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45523</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45481</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>46302</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45145</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45635</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45176</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45692</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>46121</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>45731</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>44924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45316</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45946</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44515</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46136</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45567</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>46301</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45932</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45763</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45839</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46268</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45932</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>46269</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45764</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45027</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45572</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>46272</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45987</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45987</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45845</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>44874</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>46272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46272</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45769</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>46272</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45845</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45145</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>46315</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>46315</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>46274</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>46276</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46276</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45399</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46141</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45372</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>46274</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>44907</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44523</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>46142</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45548</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>46275</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>46274</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>46149</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46149</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>46153</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44746</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45238</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>46148</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45730</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45623</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45303</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45624</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45009</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44867</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45642</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45022</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45698</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45427</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45681</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>44756</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45755</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45483</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45534</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>44817</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45176</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45758</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45077</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44525</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45715</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45715</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45082</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>44792</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44868</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45363</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44930</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45037</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45758</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44543</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45450</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>44907</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45237</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44657</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45544</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45493</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44608</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>45551</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45098</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45162</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44613</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45440</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45643</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45162</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45710</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45642</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45642</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44613</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45623</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45666</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45434</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45195</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45642</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>45572</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>44749</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45764</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44861</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45236</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>44754</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45764</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45217</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44525</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45309</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44560</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45201</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>45007</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>44954</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44522</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45036</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>43973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>43973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45383</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45383</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45034</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45209</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45383</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45716</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45733</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>46036</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>46079</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>46079</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>46079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46014</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>46272</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
